--- a/create_forecast_basic/future/iplan/Intermediates/240703_pop_2030_iplan.xlsx
+++ b/create_forecast_basic/future/iplan/Intermediates/240703_pop_2030_iplan.xlsx
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1232.051496168234</v>
+        <v>1232.051496168232</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>3800.738328186488</v>
+        <v>3800.738328186489</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3360.454071004608</v>
+        <v>3360.454071004611</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>15489.8743810636</v>
+        <v>15489.87438106359</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>8785.024859320079</v>
+        <v>8785.024859320072</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>15100.63376906175</v>
+        <v>15100.63376906176</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>9742.014064509254</v>
+        <v>9742.014064509252</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>38153.98122632317</v>
+        <v>38153.98122632319</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>28205.67768783843</v>
+        <v>28205.6776878384</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1524.431419837526</v>
+        <v>1524.431419837527</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>7468.849771014898</v>
+        <v>7468.849771014899</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>2598.100779916603</v>
+        <v>2598.100779916604</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>2356.389835782567</v>
+        <v>2356.389835782568</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>13464.20510356615</v>
+        <v>13464.20510356614</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>3175.313315680073</v>
+        <v>3175.313315680071</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>7885.201641706568</v>
+        <v>7885.201641706555</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>7274.180526998376</v>
+        <v>7274.180526998373</v>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>36330.01116296247</v>
+        <v>36330.01116296249</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>9707.940667031195</v>
+        <v>9707.9406670312</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>12267.90541141556</v>
+        <v>12267.90541141555</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>26348.07338180922</v>
+        <v>26348.07338180923</v>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>6242.115705987568</v>
+        <v>6242.115705987571</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>5260.916674641872</v>
+        <v>5260.916674641871</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>4128.338923772963</v>
+        <v>4128.338923772962</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>652.0502750507543</v>
+        <v>652.0502750507541</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>3722.840455364624</v>
+        <v>3722.840455364627</v>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>2449.742956937685</v>
+        <v>2449.742956937684</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>4157.52117207614</v>
+        <v>4157.521172076141</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>7041.18689905558</v>
+        <v>7041.186899055579</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>3487.894132597135</v>
+        <v>3487.894132597137</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>2790.810130863575</v>
+        <v>2790.810130863574</v>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>4323.27522414927</v>
+        <v>4323.275224149271</v>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>4834.718675078731</v>
+        <v>4834.71867507873</v>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>5548.019081201677</v>
+        <v>5548.019081201678</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>8219.805519892965</v>
+        <v>8219.805519892961</v>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>5756.239159726669</v>
+        <v>5756.239159726667</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>7199.647841418209</v>
+        <v>7199.647841418208</v>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>47938.81446648666</v>
+        <v>47938.81446648668</v>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>41553.03556026502</v>
+        <v>41553.035560265</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>46032.23788426784</v>
+        <v>46032.23788426782</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>59839.6098866891</v>
+        <v>59839.60988668911</v>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>74795.9999239129</v>
+        <v>74795.99992391285</v>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>1685.955238628934</v>
+        <v>1685.955238628932</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>13315.61480911469</v>
+        <v>13315.61480911468</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
-        <v>7875.518813505023</v>
+        <v>7875.518813505024</v>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>7680.015947994851</v>
+        <v>7680.015947994853</v>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
-        <v>2886.996142498469</v>
+        <v>2886.996142498468</v>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>3819.590836658151</v>
+        <v>3819.590836658152</v>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
-        <v>9721.917660304134</v>
+        <v>9721.917660304132</v>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>12559.22100002532</v>
+        <v>12559.22100002531</v>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>24575.07053038957</v>
+        <v>24575.07053038956</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>15138.50520859535</v>
+        <v>15138.50520859537</v>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>62623.56598265291</v>
+        <v>62623.56598265296</v>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>11691.62122437935</v>
+        <v>11691.62122437934</v>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>9403.773333123325</v>
+        <v>9403.773333123327</v>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>21833.54945550715</v>
+        <v>21833.54945550716</v>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
-        <v>27095.13367797237</v>
+        <v>27095.13367797236</v>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>37917.67494943826</v>
+        <v>37917.67494943827</v>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>7977.828012002438</v>
+        <v>7977.82801200244</v>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>9584.977573008026</v>
+        <v>9584.977573008027</v>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
-        <v>6368.183368581323</v>
+        <v>6368.183368581321</v>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
-        <v>3335.046834709662</v>
+        <v>3335.046834709663</v>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>3763.588281360668</v>
+        <v>3763.588281360669</v>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>4573.052179001804</v>
+        <v>4573.052179001803</v>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>9908.902741580545</v>
+        <v>9908.902741580541</v>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>11360.0882186504</v>
+        <v>11360.08821865041</v>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>8405.664389853391</v>
+        <v>8405.664389853389</v>
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>76402.35084621215</v>
+        <v>76402.35084621214</v>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>12363.16671009871</v>
+        <v>12363.1667100987</v>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>6815.652232978498</v>
+        <v>6815.652232978496</v>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
-        <v>43238.44788926775</v>
+        <v>43238.44788926774</v>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
-        <v>29645.50953607107</v>
+        <v>29645.50953607105</v>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
-        <v>41000.81603700513</v>
+        <v>41000.81603700518</v>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>30137.54893176309</v>
+        <v>30137.54893176307</v>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
